--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/46.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/46.xlsx
@@ -426,13 +426,13 @@
         <v>-11.44525455381149</v>
       </c>
       <c r="E2">
-        <v>-16.53018659200453</v>
+        <v>-20.77554946166335</v>
       </c>
       <c r="F2">
-        <v>1.105829745487095</v>
+        <v>0.8135187698568167</v>
       </c>
       <c r="G2">
-        <v>-14.0427691284025</v>
+        <v>-14.44064677347921</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.73686663991967</v>
       </c>
       <c r="E3">
-        <v>-16.26365872580908</v>
+        <v>-19.25792196747279</v>
       </c>
       <c r="F3">
-        <v>1.263095296908581</v>
+        <v>0.7249546973539104</v>
       </c>
       <c r="G3">
-        <v>-14.53361362392296</v>
+        <v>-14.74479796532116</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.853290018262726</v>
       </c>
       <c r="E4">
-        <v>-16.72024211763245</v>
+        <v>-19.03561464996224</v>
       </c>
       <c r="F4">
-        <v>1.217195459119461</v>
+        <v>1.339126170607131</v>
       </c>
       <c r="G4">
-        <v>-14.55944175942813</v>
+        <v>-14.10645435764977</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.863513203591962</v>
       </c>
       <c r="E5">
-        <v>-18.17422190964521</v>
+        <v>-20.3161991722213</v>
       </c>
       <c r="F5">
-        <v>1.256359013189016</v>
+        <v>0.58347700026238</v>
       </c>
       <c r="G5">
-        <v>-14.12747222234879</v>
+        <v>-14.96563566054725</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.784517968450987</v>
       </c>
       <c r="E6">
-        <v>-18.22449702807836</v>
+        <v>-21.50270011849701</v>
       </c>
       <c r="F6">
-        <v>1.170109399209531</v>
+        <v>1.709464385376706</v>
       </c>
       <c r="G6">
-        <v>-14.19942941114741</v>
+        <v>-14.57096705015568</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.657328934635323</v>
       </c>
       <c r="E7">
-        <v>-18.53324838592133</v>
+        <v>-21.57605234047325</v>
       </c>
       <c r="F7">
-        <v>1.141595336470367</v>
+        <v>1.471790866900277</v>
       </c>
       <c r="G7">
-        <v>-13.89621992989303</v>
+        <v>-12.94396185562956</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.513723187029512</v>
       </c>
       <c r="E8">
-        <v>-19.5618006872835</v>
+        <v>-21.16840816725078</v>
       </c>
       <c r="F8">
-        <v>1.635653536317659</v>
+        <v>1.568774465685238</v>
       </c>
       <c r="G8">
-        <v>-12.61226644940685</v>
+        <v>-13.92173634935005</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.399000350275052</v>
       </c>
       <c r="E9">
-        <v>-20.02285368295243</v>
+        <v>-24.37867509060635</v>
       </c>
       <c r="F9">
-        <v>0.9832148025247123</v>
+        <v>1.656389229144536</v>
       </c>
       <c r="G9">
-        <v>-12.69447417435718</v>
+        <v>-13.45483492754886</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.346426154004881</v>
       </c>
       <c r="E10">
-        <v>-20.04610286850781</v>
+        <v>-24.03715116636987</v>
       </c>
       <c r="F10">
-        <v>0.894778298601837</v>
+        <v>1.691066345360529</v>
       </c>
       <c r="G10">
-        <v>-11.48568855796554</v>
+        <v>-12.18554686682262</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.390049242000306</v>
       </c>
       <c r="E11">
-        <v>-20.90214295254778</v>
+        <v>-23.25135677113689</v>
       </c>
       <c r="F11">
-        <v>1.055175078805905</v>
+        <v>1.866734907002609</v>
       </c>
       <c r="G11">
-        <v>-11.75082766607647</v>
+        <v>-15.07618821793884</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.556734088522585</v>
       </c>
       <c r="E12">
-        <v>-22.2571484166489</v>
+        <v>-26.40029457100658</v>
       </c>
       <c r="F12">
-        <v>0.6141738111079212</v>
+        <v>1.837051189490691</v>
       </c>
       <c r="G12">
-        <v>-9.613164319643191</v>
+        <v>-11.85327724682701</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.8649265772778453</v>
       </c>
       <c r="E13">
-        <v>-23.87140448921513</v>
+        <v>-26.66177771715748</v>
       </c>
       <c r="F13">
-        <v>1.791095022718181</v>
+        <v>1.736172607177768</v>
       </c>
       <c r="G13">
-        <v>-10.37604505099253</v>
+        <v>-10.64993189578094</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.3356614538370948</v>
       </c>
       <c r="E14">
-        <v>-24.95997265660095</v>
+        <v>-26.25700006798187</v>
       </c>
       <c r="F14">
-        <v>1.644884862654457</v>
+        <v>1.875093134096856</v>
       </c>
       <c r="G14">
-        <v>-10.04213153899564</v>
+        <v>-10.10709316342952</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.02496693535363175</v>
       </c>
       <c r="E15">
-        <v>-23.50259650908244</v>
+        <v>-29.23430870296085</v>
       </c>
       <c r="F15">
-        <v>1.920259038367096</v>
+        <v>2.193085155948725</v>
       </c>
       <c r="G15">
-        <v>-9.644637796841385</v>
+        <v>-9.764490976743222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.219848191611522</v>
       </c>
       <c r="E16">
-        <v>-25.36487710304878</v>
+        <v>-27.46780986273075</v>
       </c>
       <c r="F16">
-        <v>1.859619231012561</v>
+        <v>1.788137751090186</v>
       </c>
       <c r="G16">
-        <v>-8.303871605664204</v>
+        <v>-9.355214367969005</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.2598023916904204</v>
       </c>
       <c r="E17">
-        <v>-25.59642250753498</v>
+        <v>-29.77965018533456</v>
       </c>
       <c r="F17">
-        <v>1.961809947291519</v>
+        <v>2.444166629206866</v>
       </c>
       <c r="G17">
-        <v>-8.853604184512012</v>
+        <v>-9.820120807062047</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1631806665554865</v>
       </c>
       <c r="E18">
-        <v>-27.24317038110625</v>
+        <v>-30.08071672278651</v>
       </c>
       <c r="F18">
-        <v>2.797886137141477</v>
+        <v>3.203880598397154</v>
       </c>
       <c r="G18">
-        <v>-8.54569107215216</v>
+        <v>-9.324918849310651</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.05060862712052507</v>
       </c>
       <c r="E19">
-        <v>-26.20609549166165</v>
+        <v>-31.26517985575876</v>
       </c>
       <c r="F19">
-        <v>2.717882413379101</v>
+        <v>2.209616055838992</v>
       </c>
       <c r="G19">
-        <v>-7.961902694738876</v>
+        <v>-9.236552271493245</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.3577165219673672</v>
       </c>
       <c r="E20">
-        <v>-27.60610493045099</v>
+        <v>-28.72104693045749</v>
       </c>
       <c r="F20">
-        <v>2.525204155487936</v>
+        <v>2.843988096576881</v>
       </c>
       <c r="G20">
-        <v>-7.192948422283006</v>
+        <v>-7.819477991729618</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7340595143499482</v>
       </c>
       <c r="E21">
-        <v>-27.67799445532276</v>
+        <v>-31.71292140208214</v>
       </c>
       <c r="F21">
-        <v>2.919324798391885</v>
+        <v>3.827903016804466</v>
       </c>
       <c r="G21">
-        <v>-8.348742310489611</v>
+        <v>-8.305033158096247</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.155463360183591</v>
       </c>
       <c r="E22">
-        <v>-28.94453617968403</v>
+        <v>-32.74333943473547</v>
       </c>
       <c r="F22">
-        <v>2.81876265242683</v>
+        <v>2.531764825318108</v>
       </c>
       <c r="G22">
-        <v>-6.708233248635595</v>
+        <v>-7.239758329050044</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.599197396315581</v>
       </c>
       <c r="E23">
-        <v>-29.23118405589556</v>
+        <v>-31.45156052472945</v>
       </c>
       <c r="F23">
-        <v>2.654315155623073</v>
+        <v>3.794675543543373</v>
       </c>
       <c r="G23">
-        <v>-6.69928535744299</v>
+        <v>-9.312483019600355</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.045163481382741</v>
       </c>
       <c r="E24">
-        <v>-30.19573316987032</v>
+        <v>-31.36243109931048</v>
       </c>
       <c r="F24">
-        <v>3.027698448965338</v>
+        <v>3.375548145483712</v>
       </c>
       <c r="G24">
-        <v>-7.336961236527035</v>
+        <v>-7.20959077803251</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.47377412973541</v>
       </c>
       <c r="E25">
-        <v>-29.52133470675202</v>
+        <v>-31.97962135028988</v>
       </c>
       <c r="F25">
-        <v>2.951182151968748</v>
+        <v>3.61194597815983</v>
       </c>
       <c r="G25">
-        <v>-6.37375208530892</v>
+        <v>-7.675730956431905</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.871883309654053</v>
       </c>
       <c r="E26">
-        <v>-30.99204947446012</v>
+        <v>-33.06503769976636</v>
       </c>
       <c r="F26">
-        <v>2.809784806515289</v>
+        <v>3.511834464061898</v>
       </c>
       <c r="G26">
-        <v>-5.584815173556033</v>
+        <v>-6.945885563743057</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.22829000698787</v>
       </c>
       <c r="E27">
-        <v>-30.29148548852551</v>
+        <v>-32.76743770916729</v>
       </c>
       <c r="F27">
-        <v>3.073137714478503</v>
+        <v>3.442957371253925</v>
       </c>
       <c r="G27">
-        <v>-6.281936943632537</v>
+        <v>-7.533421096177228</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.534751262514367</v>
       </c>
       <c r="E28">
-        <v>-30.30817291524377</v>
+        <v>-34.39992994656242</v>
       </c>
       <c r="F28">
-        <v>2.783593485973574</v>
+        <v>3.102314471139907</v>
       </c>
       <c r="G28">
-        <v>-5.290397725470177</v>
+        <v>-6.278153695174498</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.786195988529389</v>
       </c>
       <c r="E29">
-        <v>-29.71218271533128</v>
+        <v>-32.90625128716141</v>
       </c>
       <c r="F29">
-        <v>3.062547865601114</v>
+        <v>3.724444898399225</v>
       </c>
       <c r="G29">
-        <v>-4.860616763170989</v>
+        <v>-6.57554392999321</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.978858596515288</v>
       </c>
       <c r="E30">
-        <v>-28.43896375604569</v>
+        <v>-33.8729989752669</v>
       </c>
       <c r="F30">
-        <v>2.890413119299376</v>
+        <v>3.220565574624342</v>
       </c>
       <c r="G30">
-        <v>-6.089788609111455</v>
+        <v>-6.537914881149498</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.113701678055684</v>
       </c>
       <c r="E31">
-        <v>-30.21400329825427</v>
+        <v>-32.76723392783694</v>
       </c>
       <c r="F31">
-        <v>3.287940008963637</v>
+        <v>3.006150956083718</v>
       </c>
       <c r="G31">
-        <v>-4.826836587216506</v>
+        <v>-7.607583265863798</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.193503550515802</v>
       </c>
       <c r="E32">
-        <v>-30.23109149492221</v>
+        <v>-33.62000671788037</v>
       </c>
       <c r="F32">
-        <v>2.588314154437619</v>
+        <v>2.970625591647258</v>
       </c>
       <c r="G32">
-        <v>-4.947700383358652</v>
+        <v>-5.834476759571062</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.221277442617841</v>
       </c>
       <c r="E33">
-        <v>-29.74294690350239</v>
+        <v>-32.50209177468784</v>
       </c>
       <c r="F33">
-        <v>3.370960646807009</v>
+        <v>3.579351377594475</v>
       </c>
       <c r="G33">
-        <v>-5.457503777049578</v>
+        <v>-6.864983764973388</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.199561955422999</v>
       </c>
       <c r="E34">
-        <v>-30.10826795864917</v>
+        <v>-31.69377501397771</v>
       </c>
       <c r="F34">
-        <v>2.527125967862431</v>
+        <v>2.977133245963651</v>
       </c>
       <c r="G34">
-        <v>-5.044732667314551</v>
+        <v>-7.814021320276262</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.131404244077396</v>
       </c>
       <c r="E35">
-        <v>-28.63482478535144</v>
+        <v>-31.50817324253634</v>
       </c>
       <c r="F35">
-        <v>3.12565289434638</v>
+        <v>3.346397896579198</v>
       </c>
       <c r="G35">
-        <v>-5.926744709822647</v>
+        <v>-8.377174095302198</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.020369052212784</v>
       </c>
       <c r="E36">
-        <v>-28.2191652131354</v>
+        <v>-30.79438158402531</v>
       </c>
       <c r="F36">
-        <v>2.435520130256445</v>
+        <v>2.674767546798192</v>
       </c>
       <c r="G36">
-        <v>-5.454813175370832</v>
+        <v>-6.726555589823534</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.871576509163714</v>
       </c>
       <c r="E37">
-        <v>-28.51676293949747</v>
+        <v>-31.72471581263512</v>
       </c>
       <c r="F37">
-        <v>2.801421609216626</v>
+        <v>4.072329386348517</v>
       </c>
       <c r="G37">
-        <v>-5.246015922657127</v>
+        <v>-6.890770885209064</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.690450347586547</v>
       </c>
       <c r="E38">
-        <v>-26.90739309038551</v>
+        <v>-30.092819069572</v>
       </c>
       <c r="F38">
-        <v>3.034056997149227</v>
+        <v>2.728397709190238</v>
       </c>
       <c r="G38">
-        <v>-6.723681239737461</v>
+        <v>-7.451466025286977</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.482462159732228</v>
       </c>
       <c r="E39">
-        <v>-28.18095394945867</v>
+        <v>-31.01348274193843</v>
       </c>
       <c r="F39">
-        <v>3.217472450742288</v>
+        <v>3.993405853679391</v>
       </c>
       <c r="G39">
-        <v>-6.476887441365386</v>
+        <v>-8.579999524777714</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.254846967653666</v>
       </c>
       <c r="E40">
-        <v>-25.37641565482033</v>
+        <v>-30.17733850845116</v>
       </c>
       <c r="F40">
-        <v>3.179014665699919</v>
+        <v>3.440690958039866</v>
       </c>
       <c r="G40">
-        <v>-6.538830341964584</v>
+        <v>-8.255194683829842</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.015664555884425</v>
       </c>
       <c r="E41">
-        <v>-27.53040243046476</v>
+        <v>-29.04675289498517</v>
       </c>
       <c r="F41">
-        <v>3.929442636304824</v>
+        <v>3.800792208445644</v>
       </c>
       <c r="G41">
-        <v>-7.230160755988669</v>
+        <v>-8.241735112992998</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.771860578249085</v>
       </c>
       <c r="E42">
-        <v>-25.41363518268937</v>
+        <v>-27.7590767824301</v>
       </c>
       <c r="F42">
-        <v>3.196781489755162</v>
+        <v>3.566311217939605</v>
       </c>
       <c r="G42">
-        <v>-7.95094013350877</v>
+        <v>-7.772438399453419</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.528518269768486</v>
       </c>
       <c r="E43">
-        <v>-23.81731639566752</v>
+        <v>-27.74575401189953</v>
       </c>
       <c r="F43">
-        <v>3.477899565038814</v>
+        <v>3.524356065722616</v>
       </c>
       <c r="G43">
-        <v>-8.749100559065257</v>
+        <v>-9.032286385753133</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.288695914927534</v>
       </c>
       <c r="E44">
-        <v>-24.42787696069969</v>
+        <v>-28.72376401486209</v>
       </c>
       <c r="F44">
-        <v>3.771762901181938</v>
+        <v>2.889887934366001</v>
       </c>
       <c r="G44">
-        <v>-7.385260817882061</v>
+        <v>-8.897552866079215</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.052933072808791</v>
       </c>
       <c r="E45">
-        <v>-23.6550113587586</v>
+        <v>-28.09829118492266</v>
       </c>
       <c r="F45">
-        <v>3.545542390416616</v>
+        <v>2.877951160091661</v>
       </c>
       <c r="G45">
-        <v>-8.588038517598354</v>
+        <v>-10.34236331168483</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.823390694462451</v>
       </c>
       <c r="E46">
-        <v>-23.99401292297281</v>
+        <v>-21.94663548241695</v>
       </c>
       <c r="F46">
-        <v>4.181852810877056</v>
+        <v>4.445734217243255</v>
       </c>
       <c r="G46">
-        <v>-8.596700942515287</v>
+        <v>-10.41325738469819</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.598767939240992</v>
       </c>
       <c r="E47">
-        <v>-23.21987481983557</v>
+        <v>-26.42834393901009</v>
       </c>
       <c r="F47">
-        <v>3.731123196400595</v>
+        <v>3.651121129373024</v>
       </c>
       <c r="G47">
-        <v>-6.787051471715016</v>
+        <v>-9.22388019383067</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.376322101958509</v>
       </c>
       <c r="E48">
-        <v>-21.44318238461419</v>
+        <v>-24.55201601867196</v>
       </c>
       <c r="F48">
-        <v>3.993891276977431</v>
+        <v>4.236708957025245</v>
       </c>
       <c r="G48">
-        <v>-9.263241727657768</v>
+        <v>-8.82713785141353</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.15303479896614</v>
       </c>
       <c r="E49">
-        <v>-22.60620319316013</v>
+        <v>-24.64604525296722</v>
       </c>
       <c r="F49">
-        <v>3.528527723963114</v>
+        <v>3.698840061978693</v>
       </c>
       <c r="G49">
-        <v>-8.119480078909648</v>
+        <v>-10.51927037206229</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.925545402966741</v>
       </c>
       <c r="E50">
-        <v>-21.50181706606551</v>
+        <v>-24.30979247247567</v>
       </c>
       <c r="F50">
-        <v>4.119417102993252</v>
+        <v>4.35161345620237</v>
       </c>
       <c r="G50">
-        <v>-8.96405010220292</v>
+        <v>-10.92401233264136</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.694493560011453</v>
       </c>
       <c r="E51">
-        <v>-19.77078976273749</v>
+        <v>-22.9413510259938</v>
       </c>
       <c r="F51">
-        <v>3.970080684351363</v>
+        <v>3.290683561801709</v>
       </c>
       <c r="G51">
-        <v>-9.650330716247021</v>
+        <v>-10.01533380251965</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.460496290927684</v>
       </c>
       <c r="E52">
-        <v>-19.57150067860793</v>
+        <v>-21.55963662219544</v>
       </c>
       <c r="F52">
-        <v>4.330625939685041</v>
+        <v>3.752152131288063</v>
       </c>
       <c r="G52">
-        <v>-9.176968569195289</v>
+        <v>-10.48422364458586</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.2246511158325757</v>
       </c>
       <c r="E53">
-        <v>-18.63765688264218</v>
+        <v>-21.51581457922322</v>
       </c>
       <c r="F53">
-        <v>4.209546789887449</v>
+        <v>3.807775345651244</v>
       </c>
       <c r="G53">
-        <v>-8.653994352164752</v>
+        <v>-10.54237017184078</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.01021630257863775</v>
       </c>
       <c r="E54">
-        <v>-17.67247604654335</v>
+        <v>-19.83079204333912</v>
       </c>
       <c r="F54">
-        <v>4.227298703329443</v>
+        <v>3.678909542267336</v>
       </c>
       <c r="G54">
-        <v>-9.284425294045544</v>
+        <v>-10.35447430046074</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.2406328781739456</v>
       </c>
       <c r="E55">
-        <v>-17.93263234981</v>
+        <v>-19.49832959559199</v>
       </c>
       <c r="F55">
-        <v>3.782826576213729</v>
+        <v>3.881637553489265</v>
       </c>
       <c r="G55">
-        <v>-8.504564241126081</v>
+        <v>-10.99528046491249</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.461365910437482</v>
       </c>
       <c r="E56">
-        <v>-18.01601061323923</v>
+        <v>-20.02449751901722</v>
       </c>
       <c r="F56">
-        <v>4.024204553715476</v>
+        <v>3.036999358163971</v>
       </c>
       <c r="G56">
-        <v>-9.721671035392468</v>
+        <v>-10.04624947205274</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.6664439021582016</v>
       </c>
       <c r="E57">
-        <v>-16.85986855671095</v>
+        <v>-23.04815508546471</v>
       </c>
       <c r="F57">
-        <v>3.959717808142341</v>
+        <v>3.107988787849084</v>
       </c>
       <c r="G57">
-        <v>-10.15281042341727</v>
+        <v>-10.13099358126852</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.8520802590014482</v>
       </c>
       <c r="E58">
-        <v>-16.83786017303367</v>
+        <v>-18.31598125998132</v>
       </c>
       <c r="F58">
-        <v>3.470402840043478</v>
+        <v>3.413770674183687</v>
       </c>
       <c r="G58">
-        <v>-8.659654459354794</v>
+        <v>-11.279467064176</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.014915628305344</v>
       </c>
       <c r="E59">
-        <v>-17.80689926898703</v>
+        <v>-20.88232635029021</v>
       </c>
       <c r="F59">
-        <v>3.607804141145832</v>
+        <v>3.413103010057031</v>
       </c>
       <c r="G59">
-        <v>-9.928378149972806</v>
+        <v>-10.68824015748745</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.152691018436711</v>
       </c>
       <c r="E60">
-        <v>-16.7062219621047</v>
+        <v>-18.77557155854578</v>
       </c>
       <c r="F60">
-        <v>3.313402366190888</v>
+        <v>3.879109376175921</v>
       </c>
       <c r="G60">
-        <v>-10.46576677331398</v>
+        <v>-10.72336235305975</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.264680764129298</v>
       </c>
       <c r="E61">
-        <v>-15.33083836496907</v>
+        <v>-18.40353024797161</v>
       </c>
       <c r="F61">
-        <v>3.170439406346138</v>
+        <v>3.490026863815799</v>
       </c>
       <c r="G61">
-        <v>-8.830868600326619</v>
+        <v>-10.13210263415561</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.350223958194703</v>
       </c>
       <c r="E62">
-        <v>-14.63930415620574</v>
+        <v>-18.15035232315078</v>
       </c>
       <c r="F62">
-        <v>3.524208616324918</v>
+        <v>3.310002746369799</v>
       </c>
       <c r="G62">
-        <v>-9.197036520252853</v>
+        <v>-10.13362512095919</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.411805896964707</v>
       </c>
       <c r="E63">
-        <v>-14.23996520431334</v>
+        <v>-16.1169542818566</v>
       </c>
       <c r="F63">
-        <v>3.889964302622205</v>
+        <v>2.755271604471859</v>
       </c>
       <c r="G63">
-        <v>-9.03507870530022</v>
+        <v>-10.74011298912072</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.45297214225797</v>
       </c>
       <c r="E64">
-        <v>-13.5115239323875</v>
+        <v>-17.71694113282467</v>
       </c>
       <c r="F64">
-        <v>3.30627177958759</v>
+        <v>3.695645877273497</v>
       </c>
       <c r="G64">
-        <v>-8.757871264293653</v>
+        <v>-10.17882066671898</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.478087741759092</v>
       </c>
       <c r="E65">
-        <v>-13.31062271151121</v>
+        <v>-18.04466226828576</v>
       </c>
       <c r="F65">
-        <v>3.254629698962263</v>
+        <v>3.52610889114694</v>
       </c>
       <c r="G65">
-        <v>-8.751256321629812</v>
+        <v>-9.783866590051742</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.492025073099783</v>
       </c>
       <c r="E66">
-        <v>-12.63445814352992</v>
+        <v>-17.55647465636287</v>
       </c>
       <c r="F66">
-        <v>3.191183382847044</v>
+        <v>3.180514010698986</v>
       </c>
       <c r="G66">
-        <v>-8.450342054856256</v>
+        <v>-9.897383731122291</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.499437137901521</v>
       </c>
       <c r="E67">
-        <v>-13.98972625912348</v>
+        <v>-17.33896752130045</v>
       </c>
       <c r="F67">
-        <v>3.237636570061234</v>
+        <v>2.737971979631795</v>
       </c>
       <c r="G67">
-        <v>-9.324725257238644</v>
+        <v>-11.03314248048693</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.505270351352189</v>
       </c>
       <c r="E68">
-        <v>-12.93792930067994</v>
+        <v>-16.28511010718342</v>
       </c>
       <c r="F68">
-        <v>3.192054825354788</v>
+        <v>2.62428683727159</v>
       </c>
       <c r="G68">
-        <v>-8.680263811969667</v>
+        <v>-10.2692248831248</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.513902159736604</v>
       </c>
       <c r="E69">
-        <v>-13.0540891874507</v>
+        <v>-16.49278592517518</v>
       </c>
       <c r="F69">
-        <v>2.823454525396287</v>
+        <v>2.649272054874829</v>
       </c>
       <c r="G69">
-        <v>-8.333898064154683</v>
+        <v>-10.12097601184753</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.52778169162419</v>
       </c>
       <c r="E70">
-        <v>-13.84476527766395</v>
+        <v>-16.61162666855848</v>
       </c>
       <c r="F70">
-        <v>2.762526446185578</v>
+        <v>2.85954317966665</v>
       </c>
       <c r="G70">
-        <v>-8.018077207836569</v>
+        <v>-7.711867049466069</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.54707582257029</v>
       </c>
       <c r="E71">
-        <v>-13.64396368321583</v>
+        <v>-16.24776831051617</v>
       </c>
       <c r="F71">
-        <v>2.012863887060858</v>
+        <v>2.409782755051464</v>
       </c>
       <c r="G71">
-        <v>-6.092160932298934</v>
+        <v>-8.099782905888302</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.570221233330882</v>
       </c>
       <c r="E72">
-        <v>-12.89086939879223</v>
+        <v>-15.79770139278984</v>
       </c>
       <c r="F72">
-        <v>2.532694253544049</v>
+        <v>1.982842195648599</v>
       </c>
       <c r="G72">
-        <v>-7.577583057145794</v>
+        <v>-10.56375061152212</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.593995873335251</v>
       </c>
       <c r="E73">
-        <v>-14.32304458845806</v>
+        <v>-15.98174763340958</v>
       </c>
       <c r="F73">
-        <v>2.488187729726437</v>
+        <v>2.771141467174692</v>
       </c>
       <c r="G73">
-        <v>-6.638218543000164</v>
+        <v>-9.766164399738539</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.614458193557058</v>
       </c>
       <c r="E74">
-        <v>-13.10837200538064</v>
+        <v>-16.94192450572994</v>
       </c>
       <c r="F74">
-        <v>2.542278464394439</v>
+        <v>2.217321529419833</v>
       </c>
       <c r="G74">
-        <v>-5.746021588771551</v>
+        <v>-9.017087767489786</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.626384104724057</v>
       </c>
       <c r="E75">
-        <v>-11.65354538872845</v>
+        <v>-17.02176603095917</v>
       </c>
       <c r="F75">
-        <v>2.046106270935203</v>
+        <v>1.822198561958496</v>
       </c>
       <c r="G75">
-        <v>-5.851795046961811</v>
+        <v>-8.971583786903405</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.624061206287773</v>
       </c>
       <c r="E76">
-        <v>-13.82649741351701</v>
+        <v>-14.86992122352036</v>
       </c>
       <c r="F76">
-        <v>1.825026608271654</v>
+        <v>1.969918007430121</v>
       </c>
       <c r="G76">
-        <v>-6.768040073999594</v>
+        <v>-8.374070059706964</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.601898838225765</v>
       </c>
       <c r="E77">
-        <v>-13.12760896296522</v>
+        <v>-17.29694781098328</v>
       </c>
       <c r="F77">
-        <v>1.492470230743764</v>
+        <v>1.730705382319291</v>
       </c>
       <c r="G77">
-        <v>-5.789983395224992</v>
+        <v>-6.671162007456989</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.556011686706736</v>
       </c>
       <c r="E78">
-        <v>-14.12530877091313</v>
+        <v>-16.16464817010538</v>
       </c>
       <c r="F78">
-        <v>1.860936335183012</v>
+        <v>1.507978925258977</v>
       </c>
       <c r="G78">
-        <v>-6.020456397560388</v>
+        <v>-7.826654023280124</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.482851696283142</v>
       </c>
       <c r="E79">
-        <v>-13.73187042065273</v>
+        <v>-17.10433369754103</v>
       </c>
       <c r="F79">
-        <v>1.581248022036593</v>
+        <v>2.690166896816235</v>
       </c>
       <c r="G79">
-        <v>-4.490212786211512</v>
+        <v>-9.159742156008203</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.37966414932033</v>
       </c>
       <c r="E80">
-        <v>-15.0888548278952</v>
+        <v>-16.95758396884846</v>
       </c>
       <c r="F80">
-        <v>1.588859061733515</v>
+        <v>1.740763419324083</v>
       </c>
       <c r="G80">
-        <v>-5.401923165054143</v>
+        <v>-7.08673856162534</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.244606257009956</v>
       </c>
       <c r="E81">
-        <v>-14.64481530907308</v>
+        <v>-18.0852464523425</v>
       </c>
       <c r="F81">
-        <v>1.75771181638536</v>
+        <v>1.194960421293516</v>
       </c>
       <c r="G81">
-        <v>-3.997491431959057</v>
+        <v>-7.670090536571219</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.07657135088149</v>
       </c>
       <c r="E82">
-        <v>-15.10177456423908</v>
+        <v>-17.37367827456924</v>
       </c>
       <c r="F82">
-        <v>0.7589707763824692</v>
+        <v>1.446644946020896</v>
       </c>
       <c r="G82">
-        <v>-4.886229978664015</v>
+        <v>-6.58985005599239</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8775774591770055</v>
       </c>
       <c r="E83">
-        <v>-14.86022123219593</v>
+        <v>-18.62029924177078</v>
       </c>
       <c r="F83">
-        <v>1.522831552791172</v>
+        <v>1.786722899566205</v>
       </c>
       <c r="G83">
-        <v>-4.802375080490846</v>
+        <v>-7.485321669337328</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.6495144584961422</v>
       </c>
       <c r="E84">
-        <v>-17.31312804861268</v>
+        <v>-17.72000690972786</v>
       </c>
       <c r="F84">
-        <v>1.343108961079791</v>
+        <v>1.400156967375787</v>
       </c>
       <c r="G84">
-        <v>-4.060221825732521</v>
+        <v>-6.633647801367857</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3938388359841349</v>
       </c>
       <c r="E85">
-        <v>-17.2484297404651</v>
+        <v>-19.12415990223422</v>
       </c>
       <c r="F85">
-        <v>1.0575110748818</v>
+        <v>1.899531629214247</v>
       </c>
       <c r="G85">
-        <v>-3.432215706584159</v>
+        <v>-6.975790617035836</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.1124727834156738</v>
       </c>
       <c r="E86">
-        <v>-18.17556233795148</v>
+        <v>-21.04708582011128</v>
       </c>
       <c r="F86">
-        <v>0.8118057060678273</v>
+        <v>0.7996005407549794</v>
       </c>
       <c r="G86">
-        <v>-3.537326358019411</v>
+        <v>-6.320858793770671</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.1931952697237375</v>
       </c>
       <c r="E87">
-        <v>-19.81524579207079</v>
+        <v>-23.99814741974181</v>
       </c>
       <c r="F87">
-        <v>0.9641341877686285</v>
+        <v>1.708228461211729</v>
       </c>
       <c r="G87">
-        <v>-4.410610351179384</v>
+        <v>-7.279415172817494</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.5204115539068525</v>
       </c>
       <c r="E88">
-        <v>-20.38408552607029</v>
+        <v>-23.95714661607636</v>
       </c>
       <c r="F88">
-        <v>0.939998875120662</v>
+        <v>1.341984038146789</v>
       </c>
       <c r="G88">
-        <v>-3.725730818741167</v>
+        <v>-7.04898482636237</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8653886897991778</v>
       </c>
       <c r="E89">
-        <v>-22.05103945066379</v>
+        <v>-25.34262418177509</v>
       </c>
       <c r="F89">
-        <v>0.4711131039096411</v>
+        <v>1.143825301518703</v>
       </c>
       <c r="G89">
-        <v>-4.060605728654975</v>
+        <v>-6.222658394939609</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.227709223779373</v>
       </c>
       <c r="E90">
-        <v>-23.69834885501201</v>
+        <v>-26.45903340736007</v>
       </c>
       <c r="F90">
-        <v>-0.2186361260727981</v>
+        <v>1.45243689090127</v>
       </c>
       <c r="G90">
-        <v>-4.109774833723255</v>
+        <v>-5.544721927321177</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.605818058539167</v>
       </c>
       <c r="E91">
-        <v>-23.97596242557823</v>
+        <v>-27.56689740249258</v>
       </c>
       <c r="F91">
-        <v>0.1762134801456143</v>
+        <v>1.26392035084177</v>
       </c>
       <c r="G91">
-        <v>-3.498240446803305</v>
+        <v>-5.904360216344116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.997973170011271</v>
       </c>
       <c r="E92">
-        <v>-27.24041706890959</v>
+        <v>-28.90176927115559</v>
       </c>
       <c r="F92">
-        <v>0.2233757498566013</v>
+        <v>0.05208676667312236</v>
       </c>
       <c r="G92">
-        <v>-4.50967043005902</v>
+        <v>-6.259595106034278</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.401870975374302</v>
       </c>
       <c r="E93">
-        <v>-27.82435926372467</v>
+        <v>-29.78100193482585</v>
       </c>
       <c r="F93">
-        <v>0.1812209610955373</v>
+        <v>0.525439923287441</v>
       </c>
       <c r="G93">
-        <v>-4.100807255201293</v>
+        <v>-7.940847095991919</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.810152070775716</v>
       </c>
       <c r="E94">
-        <v>-29.57117056320643</v>
+        <v>-32.922542472404</v>
       </c>
       <c r="F94">
-        <v>-0.3147507674522219</v>
+        <v>-0.4165065908447104</v>
       </c>
       <c r="G94">
-        <v>-3.687990208364434</v>
+        <v>-6.075265922489352</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.220522995947726</v>
       </c>
       <c r="E95">
-        <v>-31.88997115036003</v>
+        <v>-35.40922717644397</v>
       </c>
       <c r="F95">
-        <v>-0.213405814291522</v>
+        <v>-0.3071264738768553</v>
       </c>
       <c r="G95">
-        <v>-3.771989480286218</v>
+        <v>-6.809514714510975</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.630196667622571</v>
       </c>
       <c r="E96">
-        <v>-34.50618832491539</v>
+        <v>-36.03532040732245</v>
       </c>
       <c r="F96">
-        <v>-0.4784378229802098</v>
+        <v>-0.6745480070211731</v>
       </c>
       <c r="G96">
-        <v>-4.4120573698871</v>
+        <v>-6.162434854437561</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.031749812234026</v>
       </c>
       <c r="E97">
-        <v>-34.91673751421379</v>
+        <v>-37.9656798152831</v>
       </c>
       <c r="F97">
-        <v>-0.4514852327953223</v>
+        <v>-0.7172097566327506</v>
       </c>
       <c r="G97">
-        <v>-4.290435611564721</v>
+        <v>-8.068568645193304</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.42368584994926</v>
       </c>
       <c r="E98">
-        <v>-38.57704644868864</v>
+        <v>-39.47810409283885</v>
       </c>
       <c r="F98">
-        <v>-0.6312533847138571</v>
+        <v>-0.5571219574699264</v>
       </c>
       <c r="G98">
-        <v>-4.110122643208556</v>
+        <v>-7.693377365978598</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.790415434832836</v>
       </c>
       <c r="E99">
-        <v>-41.28762570037883</v>
+        <v>-42.09853501245836</v>
       </c>
       <c r="F99">
-        <v>-0.3896534047481588</v>
+        <v>-0.452271353460579</v>
       </c>
       <c r="G99">
-        <v>-4.745226044589996</v>
+        <v>-7.713320630616903</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.136005990741197</v>
       </c>
       <c r="E100">
-        <v>-42.30791806515101</v>
+        <v>-45.26347643947116</v>
       </c>
       <c r="F100">
-        <v>-1.148225883657389</v>
+        <v>-0.3978898618341943</v>
       </c>
       <c r="G100">
-        <v>-5.551845459326731</v>
+        <v>-7.644946535761195</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.436884996479288</v>
       </c>
       <c r="E101">
-        <v>-43.93564181941606</v>
+        <v>-47.48473822497354</v>
       </c>
       <c r="F101">
-        <v>-1.316791194820463</v>
+        <v>-1.139568615930732</v>
       </c>
       <c r="G101">
-        <v>-4.716370982196239</v>
+        <v>-8.744211538941684</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.715047994520031</v>
       </c>
       <c r="E102">
-        <v>-44.53696203323558</v>
+        <v>-50.75018913258658</v>
       </c>
       <c r="F102">
-        <v>-0.9307902091987554</v>
+        <v>-0.6004016691639922</v>
       </c>
       <c r="G102">
-        <v>-6.405438841908477</v>
+        <v>-8.587477428711688</v>
       </c>
     </row>
   </sheetData>
